--- a/tests/fixtures/gisp/pp719_sample.xlsx
+++ b/tests/fixtures/gisp/pp719_sample.xlsx
@@ -416,6 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AB18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -425,7 +426,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1398,6 +1398,306 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>Департамент легкой промышленности и лесопромышленного комплекса</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ПРОИЗВОДСТВЕННАЯ КОМПАНИЯ ЛИСТОПАД"</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4706083983</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1244700033676</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>10618479</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>46828</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Бумага листовая для офисной техники марки А, массой 80 г/м2 в листах формата А4, торговой марки "Листопад"</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>17.12.14.110</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4802 56 200 0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>ТУ 17.12.14-001-86524184-2025, ГОСТ Р 57641-2017</t>
+        </is>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>СТ-1</t>
+        </is>
+      </c>
+      <c r="W15" s="1" t="n">
+        <v>45733</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5154000011_154-06-01149-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Департамент легкой промышленности и лесопромышленного комплекса</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>НЕПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "СВЕТОГОРСКИЙ ЦБК"</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4704012472</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1024700880324</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>10820764</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>47230</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Бумага рулонная марки С для офисной техники массой 80 г/м2, с  содержанием ХТММ более 10%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>17.12.14.160</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4802 61 800 0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>СТО 00253497-001-2021 с изменением 1-4</t>
+        </is>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>СТ-1</t>
+        </is>
+      </c>
+      <c r="W16" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>6154000070</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Департамент легкой промышленности и лесопромышленного комплекса</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СТАРЛЕСС ТРЕЙД"</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>7801123871</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1027800536686</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>10397488</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>47348</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Чековая лента Q-MATIC (ЧЛТ-Q)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>17.12.14.160</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>4811 90 000 0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>ТУ 17.12.14.160-015-50877062-2026</t>
+        </is>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>СТ-1</t>
+        </is>
+      </c>
+      <c r="W17" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6154000146</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Департамент легкой промышленности и лесопромышленного комплекса</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ПРОИЗВОДСТВЕННО-ТОРГОВАЯ КОМПАНИЯ "БИК"</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>7811447018</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1097847290903</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>10325594</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>47253</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Бумага для плоттеров и инженерных машин</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>17.12.14.160</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4802 55</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>ТУ 17.12.14-001-63032389-2022</t>
+        </is>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>СТ-1</t>
+        </is>
+      </c>
+      <c r="W18" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>№ 6002016019</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>Департамент легкой промышленности и лесопромышленного комплекса</t>
         </is>
